--- a/survey_templates/006_quick_website_survey--survey_templates.xlsx
+++ b/survey_templates/006_quick_website_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>manager_name_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>Manager Name 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Location 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>years_with_company</t>
+          <t>years_with_company_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Years with Company</t>
+          <t>Years With Company 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
